--- a/diseases/d180/2026-2029.xlsx
+++ b/diseases/d180/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1212,6 +1227,11 @@
       <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">

--- a/diseases/d180/2026-2029.xlsx
+++ b/diseases/d180/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.008691384892873792</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.008691384892873792</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,23 +921,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1074,11 +1044,6 @@
       <c r="R4" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1091,23 +1056,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1224,11 +1179,6 @@
       <c r="R5" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1241,22 +1191,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
